--- a/WikiViewer/Docs/PRODUCT BACKLOG.xlsx
+++ b/WikiViewer/Docs/PRODUCT BACKLOG.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F82C5351-AE2F-4389-A7AF-B474E502F87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEECF777-8CB2-47D7-A0A0-816D4A65EA2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25170" yWindow="3075" windowWidth="22455" windowHeight="12990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="To Do List" sheetId="1" r:id="rId1"/>
@@ -350,9 +350,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -605,7 +605,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -640,7 +640,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -657,9 +657,6 @@
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="16" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -667,9 +664,6 @@
     </xf>
     <xf numFmtId="14" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="16" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -696,7 +690,7 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="16" fontId="9" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -709,43 +703,26 @@
     <xf numFmtId="14" fontId="1" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="16" fontId="1" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -786,10 +763,7 @@
     <xf numFmtId="14" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -801,40 +775,19 @@
     <xf numFmtId="14" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="16" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -842,9 +795,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -852,806 +802,54 @@
     <xf numFmtId="10" fontId="1" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" indent="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
-    <cellStyle name="Heading 1" xfId="4" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
-    <cellStyle name="Title" xfId="3" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Επικεφαλίδα 1" xfId="4" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Κανονικό" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Νομισματική μονάδα" xfId="1" builtinId="4"/>
+    <cellStyle name="Ποσοστό" xfId="2" builtinId="5"/>
+    <cellStyle name="Τίτλος" xfId="3" builtinId="15" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border>
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
+  <dxfs count="31">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1671,7 +869,8 @@
           <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <border>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -1680,12 +879,6 @@
         </right>
         <top/>
         <bottom/>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1720,32 +913,790 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border>
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
     </dxf>
     <dxf>
@@ -1769,8 +1720,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="Project To Do List" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Project To Do List" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="35"/>
-      <tableStyleElement type="headerRow" dxfId="34"/>
+      <tableStyleElement type="wholeTable" dxfId="30"/>
+      <tableStyleElement type="headerRow" dxfId="29"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1785,7 +1736,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblToDoList" displayName="tblToDoList" ref="B7:K42" totalsRowCount="1" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblToDoList" displayName="tblToDoList" ref="B7:K42" totalsRowCount="1" headerRowDxfId="0" dataDxfId="28" totalsRowDxfId="27" totalsRowBorderDxfId="26">
   <autoFilter ref="B7:K41" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1799,16 +1750,16 @@
     <filterColumn colId="9" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="10">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Activity code" dataDxfId="18" totalsRowDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Περιγραφή" dataDxfId="16" totalsRowDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Sprint" dataDxfId="14" totalsRowDxfId="15"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Εκτίμηση σε ώρες" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ώρες που χρειάστηκαν / δαπανήθηκαν " totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Προτεραιότητα " dataDxfId="8" totalsRowDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{CC808B99-99CE-4502-86C5-3FD9036AA537}" name="έναρξη" dataDxfId="6" totalsRowDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{E18FB7A7-306E-4804-BD59-BB45D16E91EB}" name="Λήξη" dataDxfId="4" totalsRowDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{D6F25434-00BA-41AE-9956-BC149E133DA8}" name="Ποσοστό περάτωσης" dataDxfId="2" totalsRowDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{0860033A-E723-4CF0-BC5E-33B43CA458E6}" name="Πραγματικές ανθρωποώρες ανά ημέρα " dataDxfId="0" totalsRowDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Activity code" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Περιγραφή" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Sprint" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Εκτίμηση σε ώρες" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ώρες που χρειάστηκαν / δαπανήθηκαν " totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Προτεραιότητα " dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{CC808B99-99CE-4502-86C5-3FD9036AA537}" name="έναρξη" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{E18FB7A7-306E-4804-BD59-BB45D16E91EB}" name="Λήξη" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{D6F25434-00BA-41AE-9956-BC149E133DA8}" name="Ποσοστό περάτωσης" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{0860033A-E723-4CF0-BC5E-33B43CA458E6}" name="Πραγματικές ανθρωποώρες ανά ημέρα " dataDxfId="7" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="Project To Do List" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -2050,24 +2001,24 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" customHeight="1"/>
+  <dimension ref="A1:L109"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" style="10" customWidth="1"/>
-    <col min="2" max="2" width="22" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.85546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="47.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" style="10" customWidth="1"/>
-    <col min="10" max="10" width="25" style="10" customWidth="1"/>
-    <col min="11" max="11" width="58.28515625" style="10" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="10"/>
+    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="58.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="26.21875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="27.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="30.44140625" style="10" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2078,17 +2029,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="11" customFormat="1" ht="99.95" customHeight="1">
-      <c r="B2" s="91" t="s">
+    <row r="2" spans="1:11" s="11" customFormat="1" ht="99.9" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="B2" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-    </row>
-    <row r="3" spans="1:12" ht="26.1" customHeight="1">
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+    </row>
+    <row r="3" spans="1:11" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -2096,7 +2047,7 @@
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
     </row>
-    <row r="4" spans="1:12" ht="30" customHeight="1">
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
@@ -2108,7 +2059,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:12" s="12" customFormat="1" ht="30" customHeight="1">
+    <row r="5" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -2118,7 +2069,7 @@
       <c r="F5" s="8"/>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:12" s="12" customFormat="1" ht="60.95" customHeight="1">
+    <row r="6" spans="1:11" s="12" customFormat="1" ht="60.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
@@ -2127,313 +2078,302 @@
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
-      <c r="L6" s="80"/>
-    </row>
-    <row r="7" spans="1:12" ht="30" customHeight="1">
-      <c r="A7" s="47" t="s">
+    </row>
+    <row r="7" spans="1:11" s="86" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="98" t="s">
+      <c r="D7" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="49" t="s">
+      <c r="F7" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="50" t="s">
+      <c r="H7" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="51" t="s">
+      <c r="I7" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="82" t="s">
+      <c r="J7" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="51" t="s">
+      <c r="K7" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="43"/>
-    </row>
-    <row r="8" spans="1:12" ht="30" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="54" t="s">
+    </row>
+    <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="44"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="43"/>
-    </row>
-    <row r="9" spans="1:12" ht="30" customHeight="1">
-      <c r="A9" s="15">
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="44"/>
+    </row>
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="89">
         <v>1</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="87" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="90">
         <v>8</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="90">
         <v>10</v>
       </c>
       <c r="G9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="92">
         <v>46054</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="92">
         <v>46054</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="74">
         <v>1</v>
       </c>
-      <c r="K9" s="58" t="s">
+      <c r="K9" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="43"/>
-    </row>
-    <row r="10" spans="1:12" ht="30" customHeight="1">
-      <c r="A10" s="15">
+    </row>
+    <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="89">
         <v>2</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="87" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="90">
         <v>8</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="90">
         <v>8</v>
       </c>
       <c r="G10" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="92">
         <v>46055</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="92">
         <v>46055</v>
       </c>
-      <c r="J10" s="92">
+      <c r="J10" s="74">
         <v>1</v>
       </c>
-      <c r="K10" s="58" t="s">
+      <c r="K10" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="43"/>
-    </row>
-    <row r="11" spans="1:12" ht="30" customHeight="1">
-      <c r="A11" s="15">
+    </row>
+    <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="89">
         <v>3</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="87" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="90">
         <v>4</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="90">
         <v>4</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="92">
         <v>46056</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="92">
         <v>46056</v>
       </c>
-      <c r="J11" s="92">
+      <c r="J11" s="74">
         <v>1</v>
       </c>
-      <c r="K11" s="58" t="s">
+      <c r="K11" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="L11" s="43"/>
-    </row>
-    <row r="12" spans="1:12" ht="30" customHeight="1">
-      <c r="A12" s="15">
+    </row>
+    <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="89">
         <v>3</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="87" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="90">
         <v>16</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="90">
         <v>20</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="20">
         <v>46058</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="20">
         <v>9</v>
       </c>
-      <c r="J12" s="92">
+      <c r="J12" s="74">
         <v>0.8</v>
       </c>
-      <c r="K12" s="58" t="s">
+      <c r="K12" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L12" s="43"/>
-    </row>
-    <row r="13" spans="1:12" ht="30" customHeight="1">
-      <c r="A13" s="15">
+    </row>
+    <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="89">
         <v>4</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="88" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="91">
         <v>16</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="91">
         <v>20</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="23">
         <v>46060</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="23">
         <v>46064</v>
       </c>
-      <c r="J13" s="92">
+      <c r="J13" s="74">
         <v>0.75</v>
       </c>
-      <c r="K13" s="58" t="s">
+      <c r="K13" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="L13" s="43"/>
-    </row>
-    <row r="14" spans="1:12" ht="30" customHeight="1">
-      <c r="A14" s="15">
+    </row>
+    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="89">
         <v>5</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="88" t="s">
         <v>35</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="91">
         <v>4</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="91">
         <v>4</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="23">
         <v>46065</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="23">
         <v>46065</v>
       </c>
-      <c r="J14" s="92">
+      <c r="J14" s="74">
         <v>1</v>
       </c>
-      <c r="K14" s="58" t="s">
+      <c r="K14" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="L14" s="43"/>
-    </row>
-    <row r="15" spans="1:12" ht="30" customHeight="1">
+    </row>
+    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
       <c r="D15" s="18"/>
-      <c r="E15" s="24">
+      <c r="E15" s="91">
         <f>SUBTOTAL(109,E8:E14)</f>
         <v>56</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="91">
         <f>SUBTOTAL(109,F8:F14)</f>
         <v>66</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="59"/>
-      <c r="J15" s="92"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="43"/>
-    </row>
-    <row r="16" spans="1:12" ht="30" customHeight="1">
-      <c r="A16" s="60"/>
-      <c r="B16" s="61"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="63" t="s">
+      <c r="G15" s="21"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="74"/>
+      <c r="K15" s="49"/>
+    </row>
+    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="51"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="64"/>
-      <c r="F16" s="64"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="93"/>
-      <c r="K16" s="65"/>
-      <c r="L16" s="43"/>
-    </row>
-    <row r="17" spans="1:12" ht="30" customHeight="1">
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="56"/>
+    </row>
+    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <v>6</v>
       </c>
@@ -2443,7 +2383,7 @@
       <c r="C17" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="27" t="s">
         <v>40</v>
       </c>
       <c r="E17" s="19">
@@ -2455,1048 +2395,948 @@
       <c r="G17" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="20">
         <v>46068</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="20">
         <v>46069</v>
       </c>
-      <c r="J17" s="92">
+      <c r="J17" s="74">
         <v>1</v>
       </c>
-      <c r="K17" s="58" t="s">
+      <c r="K17" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="L17" s="43"/>
-    </row>
-    <row r="18" spans="1:12" ht="30" customHeight="1">
-      <c r="A18" s="26">
+    </row>
+    <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24">
         <v>7</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="28">
         <v>8</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="28">
         <v>8</v>
       </c>
-      <c r="G18" s="27" t="s">
+      <c r="G18" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="33">
         <v>46070</v>
       </c>
-      <c r="I18" s="35">
+      <c r="I18" s="33">
         <v>46070</v>
       </c>
-      <c r="J18" s="94">
+      <c r="J18" s="76">
         <v>1</v>
       </c>
-      <c r="K18" s="66" t="s">
+      <c r="K18" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="L18" s="43"/>
-    </row>
-    <row r="19" spans="1:12" ht="30" customHeight="1">
-      <c r="A19" s="26">
+    </row>
+    <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24">
         <v>8</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="28">
         <v>8</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="28">
         <v>8</v>
       </c>
-      <c r="G19" s="27" t="s">
+      <c r="G19" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="33">
         <v>46071</v>
       </c>
-      <c r="I19" s="35">
+      <c r="I19" s="33">
         <v>46072</v>
       </c>
-      <c r="J19" s="94">
+      <c r="J19" s="76">
         <v>1</v>
       </c>
-      <c r="K19" s="66" t="s">
+      <c r="K19" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="L19" s="43"/>
-    </row>
-    <row r="20" spans="1:12" ht="30" customHeight="1">
-      <c r="A20" s="26">
+    </row>
+    <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="24">
         <v>9</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="31">
         <v>4</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="31">
         <v>4</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="34">
         <v>46069</v>
       </c>
-      <c r="I20" s="36">
+      <c r="I20" s="34">
         <v>46069</v>
       </c>
-      <c r="J20" s="94">
+      <c r="J20" s="76">
         <v>1</v>
       </c>
-      <c r="K20" s="66" t="s">
+      <c r="K20" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="L20" s="43"/>
-    </row>
-    <row r="21" spans="1:12" ht="30" customHeight="1">
-      <c r="A21" s="26">
+    </row>
+    <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="24">
         <v>10</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="28">
         <v>8</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="28">
         <v>8</v>
       </c>
-      <c r="G21" s="27" t="s">
+      <c r="G21" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="33">
         <v>46071</v>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="33">
         <v>46072</v>
       </c>
-      <c r="J21" s="94">
+      <c r="J21" s="76">
         <v>1</v>
       </c>
-      <c r="K21" s="66" t="s">
+      <c r="K21" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="L21" s="43"/>
-    </row>
-    <row r="22" spans="1:12" ht="30" customHeight="1">
-      <c r="A22" s="26">
+    </row>
+    <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24">
         <v>11</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="31">
         <v>8</v>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="31">
         <v>8</v>
       </c>
-      <c r="G22" s="31" t="s">
+      <c r="G22" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="34">
         <v>46072</v>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="34">
         <v>46072</v>
       </c>
-      <c r="J22" s="94">
+      <c r="J22" s="76">
         <v>1</v>
       </c>
-      <c r="K22" s="66" t="s">
+      <c r="K22" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="L22" s="43"/>
-    </row>
-    <row r="23" spans="1:12" ht="30" customHeight="1">
-      <c r="A23" s="26">
+    </row>
+    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="24">
         <v>12</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="31">
         <v>8</v>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="31">
         <v>8</v>
       </c>
-      <c r="G23" s="31" t="s">
+      <c r="G23" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="34">
         <v>46073</v>
       </c>
-      <c r="I23" s="36">
+      <c r="I23" s="34">
         <v>46073</v>
       </c>
-      <c r="J23" s="94">
+      <c r="J23" s="76">
         <v>1</v>
       </c>
-      <c r="K23" s="66" t="s">
+      <c r="K23" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="L23" s="43"/>
-    </row>
-    <row r="24" spans="1:12" ht="30" customHeight="1">
-      <c r="A24" s="26">
+    </row>
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24">
         <v>13</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="28">
         <v>8</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="28">
         <v>8</v>
       </c>
-      <c r="G24" s="27" t="s">
+      <c r="G24" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="33">
         <v>46073</v>
       </c>
-      <c r="I24" s="35">
+      <c r="I24" s="33">
         <v>46073</v>
       </c>
-      <c r="J24" s="94">
+      <c r="J24" s="76">
         <v>1</v>
       </c>
-      <c r="K24" s="66" t="s">
+      <c r="K24" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="43"/>
-    </row>
-    <row r="25" spans="1:12" ht="30" customHeight="1">
-      <c r="A25" s="26">
+    </row>
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="24">
         <v>14</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="32">
         <v>4</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="32">
         <v>6</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="34">
         <v>46074</v>
       </c>
-      <c r="I25" s="36">
+      <c r="I25" s="34">
         <v>46074</v>
       </c>
-      <c r="J25" s="94">
+      <c r="J25" s="76">
         <v>1</v>
       </c>
-      <c r="K25" s="66" t="s">
+      <c r="K25" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="L25" s="43"/>
-    </row>
-    <row r="26" spans="1:12" ht="30" customHeight="1">
-      <c r="A26" s="26">
+    </row>
+    <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24">
         <v>15</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="32">
         <v>8</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="32">
         <v>8</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="H26" s="36">
+      <c r="H26" s="34">
         <v>46075</v>
       </c>
-      <c r="I26" s="36">
+      <c r="I26" s="34">
         <v>46076</v>
       </c>
-      <c r="J26" s="94">
+      <c r="J26" s="76">
         <v>1</v>
       </c>
-      <c r="K26" s="66" t="s">
+      <c r="K26" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="L26" s="43"/>
-    </row>
-    <row r="27" spans="1:12" ht="30" customHeight="1">
-      <c r="A27" s="26">
+    </row>
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="24">
         <v>16</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="32">
         <v>4</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="32">
         <v>4</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="H27" s="36">
+      <c r="H27" s="34">
         <v>46076</v>
       </c>
-      <c r="I27" s="36">
+      <c r="I27" s="34">
         <v>46076</v>
       </c>
-      <c r="J27" s="94">
+      <c r="J27" s="76">
         <v>1</v>
       </c>
-      <c r="K27" s="66" t="s">
+      <c r="K27" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="L27" s="43"/>
-    </row>
-    <row r="28" spans="1:12" ht="30" customHeight="1">
-      <c r="A28" s="26"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="34">
+    </row>
+    <row r="28" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="24"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="32">
         <f>SUBTOTAL(109,E8:E27)</f>
         <v>140</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="32">
         <f>SUBTOTAL(109,F8:F27)</f>
         <v>148</v>
       </c>
-      <c r="G28" s="31"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="94"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="43"/>
-    </row>
-    <row r="29" spans="1:12" ht="30" customHeight="1">
-      <c r="A29" s="67"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="70" t="s">
+      <c r="G28" s="29"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="76"/>
+      <c r="K28" s="57"/>
+    </row>
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="58"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="95"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="43"/>
-    </row>
-    <row r="30" spans="1:12" ht="30" customHeight="1">
-      <c r="A30" s="37">
+      <c r="E29" s="61"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="62"/>
+    </row>
+    <row r="30" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="35">
         <v>17</v>
       </c>
-      <c r="B30" s="73" t="s">
+      <c r="B30" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="74" t="s">
+      <c r="C30" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="44" t="s">
+      <c r="D30" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="E30" s="75">
+      <c r="E30" s="65">
         <v>8</v>
       </c>
-      <c r="F30" s="75">
+      <c r="F30" s="65">
         <v>8</v>
       </c>
-      <c r="G30" s="73" t="s">
+      <c r="G30" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="H30" s="76">
+      <c r="H30" s="66">
         <v>46078</v>
       </c>
-      <c r="I30" s="76">
+      <c r="I30" s="66">
         <v>46078</v>
       </c>
-      <c r="J30" s="96">
+      <c r="J30" s="78">
         <v>1</v>
       </c>
-      <c r="K30" s="77" t="s">
+      <c r="K30" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="43"/>
-    </row>
-    <row r="31" spans="1:12" ht="30" customHeight="1">
-      <c r="A31" s="37">
+    </row>
+    <row r="31" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="35">
         <v>18</v>
       </c>
-      <c r="B31" s="73" t="s">
+      <c r="B31" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="74" t="s">
+      <c r="C31" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="44" t="s">
+      <c r="D31" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="E31" s="75">
+      <c r="E31" s="65">
         <v>8</v>
       </c>
-      <c r="F31" s="75">
+      <c r="F31" s="65">
         <v>8</v>
       </c>
-      <c r="G31" s="73" t="s">
+      <c r="G31" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="H31" s="76">
+      <c r="H31" s="66">
         <v>46078</v>
       </c>
-      <c r="I31" s="76">
+      <c r="I31" s="66">
         <v>46078</v>
       </c>
-      <c r="J31" s="96">
+      <c r="J31" s="78">
         <v>1</v>
       </c>
-      <c r="K31" s="77" t="s">
+      <c r="K31" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="L31" s="43"/>
-    </row>
-    <row r="32" spans="1:12" ht="30" customHeight="1">
-      <c r="A32" s="37">
+    </row>
+    <row r="32" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="35">
         <v>19</v>
       </c>
-      <c r="B32" s="73" t="s">
+      <c r="B32" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="74" t="s">
+      <c r="C32" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="D32" s="44" t="s">
+      <c r="D32" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="E32" s="75">
+      <c r="E32" s="65">
         <v>8</v>
       </c>
-      <c r="F32" s="75">
+      <c r="F32" s="65">
         <v>8</v>
       </c>
-      <c r="G32" s="73" t="s">
+      <c r="G32" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="H32" s="76">
+      <c r="H32" s="66">
         <v>46079</v>
       </c>
-      <c r="I32" s="76">
+      <c r="I32" s="66">
         <v>46080</v>
       </c>
-      <c r="J32" s="96">
+      <c r="J32" s="78">
         <v>1</v>
       </c>
-      <c r="K32" s="77" t="s">
+      <c r="K32" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="43"/>
-    </row>
-    <row r="33" spans="1:13" ht="30" customHeight="1">
-      <c r="A33" s="37">
+    </row>
+    <row r="33" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="35">
         <v>20</v>
       </c>
-      <c r="B33" s="73" t="s">
+      <c r="B33" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="74" t="s">
+      <c r="C33" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="D33" s="78" t="s">
+      <c r="D33" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="E33" s="75">
+      <c r="E33" s="65">
         <v>4</v>
       </c>
-      <c r="F33" s="75">
+      <c r="F33" s="65">
         <v>4</v>
       </c>
-      <c r="G33" s="73" t="s">
+      <c r="G33" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="H33" s="76">
+      <c r="H33" s="66">
         <v>46081</v>
       </c>
-      <c r="I33" s="76">
+      <c r="I33" s="66">
         <v>46081</v>
       </c>
-      <c r="J33" s="96">
+      <c r="J33" s="78">
         <v>1</v>
       </c>
-      <c r="K33" s="77" t="s">
+      <c r="K33" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="L33" s="43"/>
-    </row>
-    <row r="34" spans="1:13" ht="30" customHeight="1">
-      <c r="A34" s="37">
+    </row>
+    <row r="34" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="35">
         <v>21</v>
       </c>
-      <c r="B34" s="73" t="s">
+      <c r="B34" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="74" t="s">
+      <c r="C34" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="D34" s="78" t="s">
+      <c r="D34" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="E34" s="75">
+      <c r="E34" s="65">
         <v>4</v>
       </c>
-      <c r="F34" s="75">
+      <c r="F34" s="65">
         <v>4</v>
       </c>
-      <c r="G34" s="73" t="s">
+      <c r="G34" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="H34" s="76">
+      <c r="H34" s="66">
         <v>46082</v>
       </c>
-      <c r="I34" s="76">
+      <c r="I34" s="66">
         <v>46082</v>
       </c>
-      <c r="J34" s="96">
+      <c r="J34" s="78">
         <v>1</v>
       </c>
-      <c r="K34" s="77" t="s">
+      <c r="K34" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="L34" s="43"/>
-    </row>
-    <row r="35" spans="1:13" ht="30" customHeight="1">
-      <c r="A35" s="37">
+    </row>
+    <row r="35" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="35">
         <v>22</v>
       </c>
-      <c r="B35" s="73" t="s">
+      <c r="B35" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="74" t="s">
+      <c r="C35" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="78" t="s">
+      <c r="D35" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="E35" s="75">
+      <c r="E35" s="65">
         <v>8</v>
       </c>
-      <c r="F35" s="75">
+      <c r="F35" s="65">
         <v>8</v>
       </c>
-      <c r="G35" s="73" t="s">
+      <c r="G35" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="H35" s="76">
+      <c r="H35" s="66">
         <v>46082</v>
       </c>
-      <c r="I35" s="76">
+      <c r="I35" s="66">
         <v>46083</v>
       </c>
-      <c r="J35" s="96">
+      <c r="J35" s="78">
         <v>1</v>
       </c>
-      <c r="K35" s="77" t="s">
+      <c r="K35" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="L35" s="43"/>
-    </row>
-    <row r="36" spans="1:13" ht="30" customHeight="1">
-      <c r="A36" s="37">
+    </row>
+    <row r="36" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="35">
         <v>23</v>
       </c>
-      <c r="B36" s="73" t="s">
+      <c r="B36" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="74" t="s">
+      <c r="C36" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="78" t="s">
+      <c r="D36" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="E36" s="75">
+      <c r="E36" s="65">
         <v>4</v>
       </c>
-      <c r="F36" s="75">
+      <c r="F36" s="65">
         <v>4</v>
       </c>
-      <c r="G36" s="73" t="s">
+      <c r="G36" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="H36" s="76">
+      <c r="H36" s="66">
         <v>46083</v>
       </c>
-      <c r="I36" s="76">
+      <c r="I36" s="66">
         <v>46056</v>
       </c>
-      <c r="J36" s="96">
+      <c r="J36" s="78">
         <v>1</v>
       </c>
-      <c r="K36" s="77" t="s">
+      <c r="K36" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="L36" s="43"/>
-    </row>
-    <row r="37" spans="1:13" ht="30" customHeight="1">
-      <c r="A37" s="37">
+    </row>
+    <row r="37" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="35">
         <v>24</v>
       </c>
-      <c r="B37" s="73" t="s">
+      <c r="B37" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="74" t="s">
+      <c r="C37" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="D37" s="78" t="s">
+      <c r="D37" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="E37" s="75">
+      <c r="E37" s="65">
         <v>4</v>
       </c>
-      <c r="F37" s="75">
+      <c r="F37" s="65">
         <v>4</v>
       </c>
-      <c r="G37" s="73" t="s">
+      <c r="G37" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="H37" s="76">
+      <c r="H37" s="66">
         <v>46083</v>
       </c>
-      <c r="I37" s="76">
+      <c r="I37" s="66">
         <v>46083</v>
       </c>
-      <c r="J37" s="96">
+      <c r="J37" s="78">
         <v>1</v>
       </c>
-      <c r="K37" s="77" t="s">
+      <c r="K37" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="L37" s="43"/>
-    </row>
-    <row r="38" spans="1:13" ht="30" customHeight="1">
-      <c r="A38" s="37">
+    </row>
+    <row r="38" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="35">
         <v>25</v>
       </c>
-      <c r="B38" s="73" t="s">
+      <c r="B38" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="74" t="s">
+      <c r="C38" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="78" t="s">
+      <c r="D38" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="E38" s="75">
+      <c r="E38" s="65">
         <v>8</v>
       </c>
-      <c r="F38" s="75">
+      <c r="F38" s="65">
         <v>8</v>
       </c>
-      <c r="G38" s="73" t="s">
+      <c r="G38" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="H38" s="76">
+      <c r="H38" s="66">
         <v>46083</v>
       </c>
-      <c r="I38" s="76">
+      <c r="I38" s="66">
         <v>46083</v>
       </c>
-      <c r="J38" s="96">
+      <c r="J38" s="78">
         <v>1</v>
       </c>
-      <c r="K38" s="77" t="s">
+      <c r="K38" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="L38" s="43"/>
-    </row>
-    <row r="39" spans="1:13" ht="30" customHeight="1">
-      <c r="A39" s="37">
+    </row>
+    <row r="39" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="35">
         <v>26</v>
       </c>
-      <c r="B39" s="73" t="s">
+      <c r="B39" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="74" t="s">
+      <c r="C39" s="64" t="s">
         <v>93</v>
       </c>
-      <c r="D39" s="78" t="s">
+      <c r="D39" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="75">
+      <c r="E39" s="65">
         <v>4</v>
       </c>
-      <c r="F39" s="75">
+      <c r="F39" s="65">
         <v>4</v>
       </c>
-      <c r="G39" s="73" t="s">
+      <c r="G39" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="H39" s="76">
+      <c r="H39" s="66">
         <v>46084</v>
       </c>
-      <c r="I39" s="76">
+      <c r="I39" s="66">
         <v>46084</v>
       </c>
-      <c r="J39" s="96">
+      <c r="J39" s="78">
         <v>1</v>
       </c>
-      <c r="K39" s="77" t="s">
+      <c r="K39" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="L39" s="43"/>
-    </row>
-    <row r="40" spans="1:13" ht="30" customHeight="1">
-      <c r="A40" s="37">
+    </row>
+    <row r="40" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="35">
         <v>27</v>
       </c>
-      <c r="B40" s="73" t="s">
+      <c r="B40" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="C40" s="74" t="s">
+      <c r="C40" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="D40" s="78" t="s">
+      <c r="D40" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="E40" s="75">
+      <c r="E40" s="65">
         <v>4</v>
       </c>
-      <c r="F40" s="75">
+      <c r="F40" s="65">
         <v>4</v>
       </c>
-      <c r="G40" s="73" t="s">
+      <c r="G40" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="H40" s="76">
+      <c r="H40" s="66">
         <v>46084</v>
       </c>
-      <c r="I40" s="76">
+      <c r="I40" s="66">
         <v>46084</v>
       </c>
-      <c r="J40" s="96">
+      <c r="J40" s="78">
         <v>1</v>
       </c>
-      <c r="K40" s="77" t="s">
+      <c r="K40" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="L40" s="43"/>
-    </row>
-    <row r="41" spans="1:13" ht="30" customHeight="1">
-      <c r="A41" s="42">
+    </row>
+    <row r="41" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="39">
         <v>28</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="38" t="s">
+      <c r="C41" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="D41" s="39" t="s">
+      <c r="D41" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="E41" s="40">
+      <c r="E41" s="38">
         <v>32</v>
       </c>
-      <c r="F41" s="40">
+      <c r="F41" s="38">
         <v>32</v>
       </c>
-      <c r="G41" s="41" t="s">
+      <c r="G41" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="45">
+      <c r="H41" s="41">
         <v>46080</v>
       </c>
-      <c r="I41" s="45">
+      <c r="I41" s="41">
         <v>46084</v>
       </c>
-      <c r="J41" s="46">
+      <c r="J41" s="42">
         <v>1</v>
       </c>
-      <c r="K41" s="77" t="s">
+      <c r="K41" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="L41" s="43"/>
-    </row>
-    <row r="42" spans="1:13" ht="30" customHeight="1">
-      <c r="A42" s="37"/>
-      <c r="B42" s="73"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="78"/>
-      <c r="E42" s="75">
-        <f ca="1">SUBTOTAL(109,tblToDoList[Εκτίμηση σε ώρες])</f>
+    </row>
+    <row r="42" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="35"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="65">
+        <f>SUBTOTAL(109,tblToDoList[Εκτίμηση σε ώρες])</f>
         <v>236</v>
       </c>
-      <c r="F42" s="75">
-        <f ca="1">SUBTOTAL(109,tblToDoList[Ώρες που χρειάστηκαν / δαπανήθηκαν ])</f>
+      <c r="F42" s="65">
+        <f>SUBTOTAL(109,tblToDoList[Ώρες που χρειάστηκαν / δαπανήθηκαν ])</f>
         <v>244</v>
       </c>
-      <c r="G42" s="73"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="97"/>
-      <c r="K42" s="79"/>
-      <c r="L42" s="81"/>
-    </row>
-    <row r="43" spans="1:13" ht="30" customHeight="1">
-      <c r="A43" s="81"/>
-      <c r="B43" s="84"/>
-      <c r="C43" s="85"/>
-      <c r="D43" s="88" t="s">
+      <c r="G42" s="63"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="79"/>
+      <c r="K42" s="68"/>
+      <c r="L42" s="69"/>
+    </row>
+    <row r="43" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="69"/>
+      <c r="D43" s="71" t="s">
         <v>100</v>
       </c>
-      <c r="E43" s="89">
+      <c r="E43" s="72">
         <v>236</v>
       </c>
-      <c r="F43" s="90">
+      <c r="F43" s="73">
         <v>244</v>
       </c>
-      <c r="G43" s="84"/>
-      <c r="H43" s="43"/>
-      <c r="I43" s="43"/>
-      <c r="J43" s="43"/>
-      <c r="K43" s="43"/>
-      <c r="L43" s="43"/>
-    </row>
-    <row r="44" spans="1:13" ht="30" customHeight="1">
-      <c r="A44" s="43"/>
-      <c r="B44" s="84"/>
-      <c r="C44" s="85"/>
-      <c r="D44" s="86"/>
-      <c r="E44" s="87"/>
-      <c r="F44" s="87"/>
-      <c r="G44" s="84"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="43"/>
-      <c r="L44" s="43"/>
-      <c r="M44" s="43"/>
-    </row>
-    <row r="45" spans="1:13" ht="30" customHeight="1">
-      <c r="A45" s="43"/>
-      <c r="B45" s="84"/>
-      <c r="C45" s="85"/>
-      <c r="D45" s="86"/>
-      <c r="E45" s="87"/>
-      <c r="F45" s="87"/>
-      <c r="G45" s="84"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="43"/>
-      <c r="M45" s="43"/>
-    </row>
-    <row r="46" spans="1:13" ht="30" customHeight="1">
-      <c r="A46" s="43"/>
-      <c r="B46" s="84"/>
-      <c r="C46" s="85"/>
-      <c r="D46" s="86"/>
-      <c r="E46" s="87"/>
-      <c r="F46" s="87"/>
-      <c r="G46" s="84"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="43"/>
-      <c r="J46" s="43"/>
-      <c r="K46" s="43"/>
-      <c r="L46" s="43"/>
-      <c r="M46" s="43"/>
-    </row>
-    <row r="47" spans="1:13" ht="30" customHeight="1"/>
-    <row r="48" spans="1:13" ht="30" customHeight="1"/>
-    <row r="49" ht="30" customHeight="1"/>
-    <row r="50" ht="30" customHeight="1"/>
-    <row r="51" ht="30" customHeight="1"/>
-    <row r="52" ht="30" customHeight="1"/>
-    <row r="53" ht="30" customHeight="1"/>
-    <row r="54" ht="30" customHeight="1"/>
-    <row r="55" ht="30" customHeight="1"/>
-    <row r="56" ht="30" customHeight="1"/>
-    <row r="57" ht="30" customHeight="1"/>
-    <row r="58" ht="30" customHeight="1"/>
-    <row r="59" ht="30" customHeight="1"/>
-    <row r="60" ht="30" customHeight="1"/>
-    <row r="61" ht="30" customHeight="1"/>
-    <row r="62" ht="30" customHeight="1"/>
-    <row r="63" ht="30" customHeight="1"/>
-    <row r="64" ht="30" customHeight="1"/>
-    <row r="65" ht="30" customHeight="1"/>
-    <row r="66" ht="30" customHeight="1"/>
-    <row r="67" ht="30" customHeight="1"/>
-    <row r="68" ht="30" customHeight="1"/>
-    <row r="69" ht="30" customHeight="1"/>
-    <row r="70" ht="30" customHeight="1"/>
-    <row r="71" ht="30" customHeight="1"/>
-    <row r="72" ht="30" customHeight="1"/>
-    <row r="73" ht="30" customHeight="1"/>
-    <row r="74" ht="30" customHeight="1"/>
-    <row r="75" ht="30" customHeight="1"/>
-    <row r="76" ht="30" customHeight="1"/>
-    <row r="77" ht="30" customHeight="1"/>
-    <row r="78" ht="30" customHeight="1"/>
-    <row r="79" ht="30" customHeight="1"/>
-    <row r="80" ht="30" customHeight="1"/>
-    <row r="81" ht="30" customHeight="1"/>
-    <row r="82" ht="30" customHeight="1"/>
-    <row r="83" ht="30" customHeight="1"/>
-    <row r="84" ht="30" customHeight="1"/>
-    <row r="85" ht="30" customHeight="1"/>
-    <row r="86" ht="30" customHeight="1"/>
-    <row r="87" ht="30" customHeight="1"/>
-    <row r="88" ht="30" customHeight="1"/>
-    <row r="89" ht="30" customHeight="1"/>
-    <row r="90" ht="30" customHeight="1"/>
-    <row r="91" ht="30" customHeight="1"/>
-    <row r="92" ht="30" customHeight="1"/>
-    <row r="93" ht="30" customHeight="1"/>
-    <row r="94" ht="30" customHeight="1"/>
-    <row r="95" ht="30" customHeight="1"/>
-    <row r="96" ht="30" customHeight="1"/>
-    <row r="97" ht="30" customHeight="1"/>
-    <row r="98" ht="30" customHeight="1"/>
-    <row r="99" ht="30" customHeight="1"/>
-    <row r="100" ht="30" customHeight="1"/>
-    <row r="101" ht="30" customHeight="1"/>
-    <row r="102" ht="30" customHeight="1"/>
-    <row r="103" ht="30" customHeight="1"/>
-    <row r="104" ht="30" customHeight="1"/>
-    <row r="105" ht="30" customHeight="1"/>
-    <row r="106" ht="30" customHeight="1"/>
-    <row r="107" ht="30" customHeight="1"/>
-    <row r="108" ht="30" customHeight="1"/>
-    <row r="109" ht="30" customHeight="1"/>
+    </row>
+    <row r="44" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="B8:G41">
-    <cfRule type="expression" dxfId="33" priority="11">
+    <cfRule type="expression" dxfId="5" priority="11">
       <formula>AND($C8&gt;=valHStart, $C8&lt;=valHEnd)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D25:D26">
+    <cfRule type="expression" dxfId="4" priority="6">
+      <formula>AND($C25&gt;=valHStart, $C25&lt;=valHEnd)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D33:D41">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>AND($C33&gt;=valHStart, $C33&lt;=valHEnd)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H9:H11">
-    <cfRule type="expression" dxfId="32" priority="9">
+    <cfRule type="expression" dxfId="2" priority="9">
       <formula>AND($C9&gt;=valHStart, $C9&lt;=valHEnd)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="expression" dxfId="31" priority="8">
+    <cfRule type="expression" dxfId="1" priority="8">
       <formula>AND($C9&gt;=valHStart, $C9&lt;=valHEnd)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D25">
-    <cfRule type="expression" dxfId="30" priority="7">
-      <formula>AND($C25&gt;=valHStart, $C25&lt;=valHEnd)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D26">
-    <cfRule type="expression" dxfId="29" priority="6">
-      <formula>AND($C26&gt;=valHStart, $C26&lt;=valHEnd)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D33">
-    <cfRule type="expression" dxfId="28" priority="5">
-      <formula>AND($C33&gt;=valHStart, $C33&lt;=valHEnd)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D34">
-    <cfRule type="expression" dxfId="27" priority="4">
-      <formula>AND($C34&gt;=valHStart, $C34&lt;=valHEnd)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D35:D41">
-    <cfRule type="expression" dxfId="26" priority="3">
-      <formula>AND($C35&gt;=valHStart, $C35&lt;=valHEnd)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D36">
-    <cfRule type="expression" dxfId="25" priority="2">
-      <formula>AND($C36&gt;=valHStart, $C36&lt;=valHEnd)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D37">
-    <cfRule type="expression" dxfId="24" priority="1">
-      <formula>AND($C37&gt;=valHStart, $C37&lt;=valHEnd)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="13">
@@ -3548,15 +3388,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3868,16 +3699,54 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C02396-02E5-4855-9EEB-E6D78D6179A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C02396-02E5-4855-9EEB-E6D78D6179A2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76FDD323-8E7B-49B7-A576-85D534BC045A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFC58ABA-4870-4323-82D0-EF10BC9FA681}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFC58ABA-4870-4323-82D0-EF10BC9FA681}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76FDD323-8E7B-49B7-A576-85D534BC045A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
